--- a/analysis/experiment_analysis.xlsx
+++ b/analysis/experiment_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\T.K.KRISHNA\BITS Business Analytics and AI Course\Assignments\Capstone project\part-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59E2020-BA2A-4F77-B943-D5186E991421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23763D7-FC01-4D6D-894C-8761969E6573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4A79C09-4C3A-4F6E-AF3F-75832ADBBDE2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="8" xr2:uid="{C4A79C09-4C3A-4F6E-AF3F-75832ADBBDE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Group Counts" sheetId="5" r:id="rId6"/>
     <sheet name="Revenue Outliers" sheetId="2" r:id="rId7"/>
     <sheet name="Paid Conversion Rate(North star" sheetId="8" r:id="rId8"/>
+    <sheet name="Hypothesis Test" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9884" uniqueCount="1459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9902" uniqueCount="1470">
   <si>
     <t>user_id</t>
   </si>
@@ -4409,16 +4410,50 @@
   </si>
   <si>
     <t>Treatment Group</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Not Paid</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>The Treatment group has a significantly higher Paid Conversion Rate than the Control group. Since the p-value is less than 0.05, the improvement is statistically significant. The business can consider launching the new onboarding campaign while continuing to monitor guardrail metrics.</t>
+  </si>
+  <si>
+    <t>Business Interpretation</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Values</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4432,8 +4467,16 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4443,6 +4486,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF155E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -4458,18 +4507,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4500,6 +4555,108 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4511,6 +4668,46 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60952E36-2F96-416F-A7CB-B0470129CA61}" name="Table1" displayName="Table1" ref="A1:D4" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:D4" xr:uid="{60952E36-2F96-416F-A7CB-B0470129CA61}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6BE02A0F-862C-4C95-AC36-2335934BBE7B}" name="Group" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{6C9DC445-4EBE-4508-A1D2-2AAF939DE972}" name="Paid"/>
+    <tableColumn id="3" xr3:uid="{400259E8-B42E-4406-919A-90649C922D8A}" name="Not Paid"/>
+    <tableColumn id="4" xr3:uid="{AFE18602-0D3C-4B86-BA7E-53348406F047}" name="Grand Total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9BFC9015-D720-4D9C-B750-7F7213762B51}" name="Table2" displayName="Table2" ref="F1:H3" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="F1:H3" xr:uid="{9BFC9015-D720-4D9C-B750-7F7213762B51}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{D8DEC4A5-9A31-45C4-855D-FFE13A57CDEA}" name="Group" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{F19DD35D-82FD-4FE9-A028-C8BEC5072274}" name="Paid" dataDxfId="5">
+      <calculatedColumnFormula>((B2+C2)*B3)/D3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{25A9D78A-76B1-482F-B5D9-C801EC5601C4}" name="Not Paid" dataDxfId="4">
+      <calculatedColumnFormula>((B2+C2)*C3)/D3</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6D30FA92-AD71-4FA5-8CAE-176BC2A87EE3}" name="Table4" displayName="Table4" ref="J1:K4" totalsRowShown="0">
+  <autoFilter ref="J1:K4" xr:uid="{6D30FA92-AD71-4FA5-8CAE-176BC2A87EE3}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{BBABBCB5-5CEE-47E2-B312-591FD7842984}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{4288A4EC-300C-4A06-8C4C-4AF2CFB08785}" name="Values"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -78704,4 +78901,144 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94882CB8-1DF8-4149-BB71-1B45ED18B45B}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" customWidth="1"/>
+    <col min="11" max="11" width="20.453125" customWidth="1"/>
+    <col min="12" max="12" width="52.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4">
+        <v>671</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="4">
+        <f>((B2+C2)*B4)/D4</f>
+        <v>35.4375</v>
+      </c>
+      <c r="H2" s="4">
+        <f>((B2+C2)*C4)/D4</f>
+        <v>657.5625</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K2" s="5">
+        <f>_xlfn.CHISQ.TEST(B2:C3,G2:H3)</f>
+        <v>1.1464793738873366E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B3" s="4">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4">
+        <v>665</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="G3" s="4">
+        <f>((B3+C3)*B4)/D4</f>
+        <v>36.5625</v>
+      </c>
+      <c r="H3" s="4">
+        <f>((B3+C3)*C4)/D4</f>
+        <v>678.4375</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="K3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B4">
+        <f>SUM(B2:B3)</f>
+        <v>72</v>
+      </c>
+      <c r="C4">
+        <f>SUM(C2:C3)</f>
+        <v>1336</v>
+      </c>
+      <c r="D4">
+        <f>SUM(B4:C4)</f>
+        <v>1408</v>
+      </c>
+      <c r="K4" s="6" t="str">
+        <f>IF(K2&lt;K3,"Reject Null Hypothesis","Fail to Reject Null Hypothesis")</f>
+        <v>Reject Null Hypothesis</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="64.5" customHeight="1">
+      <c r="K6" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>